--- a/data/source/weekly/cs-en-us-078pct.xlsx
+++ b/data/source/weekly/cs-en-us-078pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
-      </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>1</v>
@@ -936,20 +936,20 @@
       <c r="C16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F16" s="15">
         <v>1</v>
       </c>
-      <c r="E16" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="15">
+      <c r="G16" s="15">
         <v>3</v>
       </c>
-      <c r="G16" s="15">
-        <v>4</v>
-      </c>
       <c r="H16" s="14">
-        <v>-25</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="15">
         <v>4</v>
@@ -961,54 +961,54 @@
         <v>-20</v>
       </c>
       <c r="L16" s="14">
-        <v>-71.428571428571</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="M16" s="14">
-        <v>-78.947368421052</v>
+        <v>-80</v>
       </c>
       <c r="N16" s="14">
-        <v>-96.078431372549</v>
+        <v>-96.638655462184</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>4</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="15">
         <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H17" s="14">
-        <v>33.333333333333</v>
+        <v>30</v>
       </c>
       <c r="I17" s="15">
         <v>17</v>
       </c>
       <c r="J17" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K17" s="14">
-        <v>-5.555555555555</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="L17" s="14">
-        <v>54.545454545454</v>
+        <v>21.428571428571</v>
       </c>
       <c r="M17" s="14">
         <v>466.666666666667</v>
       </c>
       <c r="N17" s="14">
-        <v>-15</v>
+        <v>-19.047619047619</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="15">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="15">
+        <v>3</v>
+      </c>
+      <c r="E18" s="14">
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="15">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H18" s="14">
-        <v>-78.571428571428</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="I18" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K18" s="14">
-        <v>-46.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="14">
-        <v>-52.941176470588</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="M18" s="14">
-        <v>-42.857142857142</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="N18" s="14">
-        <v>-91.578947368421</v>
+        <v>-92.035398230088</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E19" s="14">
-        <v>-20</v>
+        <v>500</v>
       </c>
       <c r="F19" s="15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G19" s="15">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H19" s="14">
-        <v>-16.666666666666</v>
+        <v>35.714285714285</v>
       </c>
       <c r="I19" s="15">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J19" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K19" s="14">
-        <v>-22.580645161290</v>
+        <v>-6.25</v>
       </c>
       <c r="L19" s="14">
-        <v>-46.666666666666</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M19" s="14">
-        <v>-51.020408163265</v>
+        <v>-43.396226415094</v>
       </c>
       <c r="N19" s="14">
-        <v>-46.666666666666</v>
+        <v>-42.307692307692</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H20" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I20" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J20" s="15">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K20" s="14">
-        <v>66.666666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>-73.684210526315</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M20" s="14">
-        <v>-16.666666666666</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.323529411764</v>
+        <v>-95.731707317073</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D21" s="17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E21" s="18">
-        <v>33.333333333333</v>
+        <v>12.5</v>
       </c>
       <c r="F21" s="17">
         <v>41</v>
       </c>
       <c r="G21" s="17">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="H21" s="18">
-        <v>-19.607843137254</v>
+        <v>-8.888888888888</v>
       </c>
       <c r="I21" s="17">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="J21" s="17">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.270270270270</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="L21" s="18">
-        <v>-45.370370370370</v>
+        <v>-44.262295081967</v>
       </c>
       <c r="M21" s="18">
-        <v>-35.164835164835</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.432098765432</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,37 +1180,37 @@
         <v>29</v>
       </c>
       <c r="C22" s="15">
-        <v>2</v>
-      </c>
-      <c r="D22" s="15">
         <v>1</v>
       </c>
-      <c r="E22" s="14">
-        <v>100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H22" s="14">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="15">
         <v>5</v>
       </c>
       <c r="K22" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D24" s="15">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E24" s="14">
-        <v>-52.173913043478</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="F24" s="15">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G24" s="15">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="H24" s="14">
-        <v>-11.224489795918</v>
+        <v>7.317073170731</v>
       </c>
       <c r="I24" s="15">
-        <v>123</v>
+        <v>149</v>
       </c>
       <c r="J24" s="15">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="K24" s="14">
-        <v>-6.106870229007</v>
+        <v>-5.095541401273</v>
       </c>
       <c r="L24" s="14">
-        <v>16.037735849056</v>
+        <v>25.210084033613</v>
       </c>
       <c r="M24" s="14">
-        <v>41.379310344827</v>
+        <v>56.842105263157</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D25" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E25" s="14">
-        <v>-55.555555555555</v>
+        <v>-20</v>
       </c>
       <c r="F25" s="15">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G25" s="15">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H25" s="14">
-        <v>-20</v>
+        <v>1.612903225806</v>
       </c>
       <c r="I25" s="15">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="J25" s="15">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="K25" s="14">
-        <v>-6.741573033707</v>
+        <v>-7.339449541284</v>
       </c>
       <c r="L25" s="14">
-        <v>33.870967741935</v>
+        <v>40.277777777777</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D26" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F26" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G26" s="15">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H26" s="14">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="I26" s="15">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J26" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K26" s="14">
-        <v>-12</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L26" s="14">
-        <v>29.411764705882</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M26" s="14">
-        <v>-18.518518518518</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>2</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-50</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="15">
         <v>2</v>
-      </c>
-      <c r="D28" s="15">
-        <v>2</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
-      </c>
-      <c r="F28" s="15">
-        <v>4</v>
       </c>
       <c r="G28" s="15">
         <v>6</v>
       </c>
       <c r="H28" s="14">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="15">
         <v>5</v>
       </c>
       <c r="J28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>-28.571428571428</v>
+        <v>-37.5</v>
       </c>
       <c r="L28" s="14">
-        <v>-61.538461538461</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-078pct.xlsx
+++ b/data/source/weekly/cs-en-us-078pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -926,62 +926,62 @@
         <v>21</v>
       </c>
       <c r="N15" s="14">
-        <v>-83.333333333333</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="15">
+        <v>2</v>
+      </c>
+      <c r="D16" s="15">
+        <v>1</v>
+      </c>
+      <c r="E16" s="14">
+        <v>100</v>
       </c>
       <c r="F16" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
         <v>3</v>
       </c>
       <c r="H16" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I16" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J16" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K16" s="14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L16" s="14">
-        <v>-73.333333333333</v>
+        <v>-62.5</v>
       </c>
       <c r="M16" s="14">
-        <v>-80</v>
+        <v>-70</v>
       </c>
       <c r="N16" s="14">
-        <v>-96.638655462184</v>
+        <v>-95.488721804511</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="15">
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-100</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="15">
         <v>13</v>
@@ -993,22 +993,22 @@
         <v>30</v>
       </c>
       <c r="I17" s="15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J17" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K17" s="14">
-        <v>-10.526315789473</v>
+        <v>-12.5</v>
       </c>
       <c r="L17" s="14">
-        <v>21.428571428571</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="M17" s="14">
-        <v>466.666666666667</v>
+        <v>425</v>
       </c>
       <c r="N17" s="14">
-        <v>-19.047619047619</v>
+        <v>-16</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E18" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H18" s="14">
-        <v>-83.333333333333</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I18" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J18" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K18" s="14">
         <v>-50</v>
       </c>
       <c r="L18" s="14">
-        <v>-52.631578947368</v>
+        <v>-50</v>
       </c>
       <c r="M18" s="14">
-        <v>-35.714285714285</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.035398230088</v>
+        <v>-90.677966101694</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>500</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G19" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H19" s="14">
-        <v>35.714285714285</v>
+        <v>27.777777777777</v>
       </c>
       <c r="I19" s="15">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J19" s="15">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="K19" s="14">
-        <v>-6.25</v>
+        <v>-7.5</v>
       </c>
       <c r="L19" s="14">
-        <v>-41.176470588235</v>
+        <v>-37.288135593220</v>
       </c>
       <c r="M19" s="14">
-        <v>-43.396226415094</v>
+        <v>-33.928571428571</v>
       </c>
       <c r="N19" s="14">
-        <v>-42.307692307692</v>
+        <v>-35.087719298245</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
         <v>5</v>
       </c>
       <c r="G20" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I20" s="15">
+        <v>8</v>
+      </c>
+      <c r="J20" s="15">
         <v>7</v>
       </c>
-      <c r="J20" s="15">
-        <v>6</v>
-      </c>
       <c r="K20" s="14">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L20" s="14">
-        <v>-66.666666666666</v>
+        <v>-65.217391304347</v>
       </c>
       <c r="M20" s="14">
-        <v>16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.731707317073</v>
+        <v>-95.628415300546</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>12.5</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="F21" s="17">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="G21" s="17">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H21" s="18">
-        <v>-8.888888888888</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="J21" s="17">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.073170731707</v>
+        <v>-16.831683168316</v>
       </c>
       <c r="L21" s="18">
-        <v>-44.262295081967</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M21" s="18">
-        <v>-29.166666666666</v>
+        <v>-20</v>
       </c>
       <c r="N21" s="18">
-        <v>-85.714285714285</v>
+        <v>-83.969465648855</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="15">
         <v>5</v>
       </c>
       <c r="K22" s="14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L22" s="14">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="14">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,32 +1223,32 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>-100</v>
       </c>
       <c r="F23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="G23" s="15">
+        <v>1</v>
+      </c>
+      <c r="H23" s="14">
+        <v>-100</v>
       </c>
       <c r="I23" s="15">
         <v>1</v>
       </c>
       <c r="J23" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K23" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L23" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D24" s="15">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E24" s="14">
-        <v>-3.846153846153</v>
+        <v>-53.125</v>
       </c>
       <c r="F24" s="15">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G24" s="15">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="H24" s="14">
-        <v>7.317073170731</v>
+        <v>-22.448979591836</v>
       </c>
       <c r="I24" s="15">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="J24" s="15">
-        <v>157</v>
+        <v>189</v>
       </c>
       <c r="K24" s="14">
-        <v>-5.095541401273</v>
+        <v>-13.227513227513</v>
       </c>
       <c r="L24" s="14">
-        <v>25.210084033613</v>
+        <v>19.708029197080</v>
       </c>
       <c r="M24" s="14">
-        <v>56.842105263157</v>
+        <v>54.716981132075</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D25" s="15">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E25" s="14">
-        <v>-20</v>
+        <v>-82.758620689655</v>
       </c>
       <c r="F25" s="15">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="G25" s="15">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="H25" s="14">
-        <v>1.612903225806</v>
+        <v>-40</v>
       </c>
       <c r="I25" s="15">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J25" s="15">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="K25" s="14">
-        <v>-7.339449541284</v>
+        <v>-23.188405797101</v>
       </c>
       <c r="L25" s="14">
-        <v>40.277777777777</v>
+        <v>26.190476190476</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="G26" s="15">
         <v>8</v>
       </c>
       <c r="H26" s="14">
-        <v>150</v>
+        <v>187.5</v>
       </c>
       <c r="I26" s="15">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J26" s="15">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="K26" s="14">
-        <v>-11.111111111111</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="L26" s="14">
-        <v>14.285714285714</v>
+        <v>25</v>
       </c>
       <c r="M26" s="14">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="15">
         <v>2</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
+        <v>5</v>
+      </c>
+      <c r="H28" s="14">
+        <v>-40</v>
+      </c>
+      <c r="I28" s="15">
         <v>6</v>
-      </c>
-      <c r="H28" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="I28" s="15">
-        <v>5</v>
       </c>
       <c r="J28" s="15">
         <v>8</v>
       </c>
       <c r="K28" s="14">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="L28" s="14">
-        <v>-64.285714285714</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-078pct.xlsx
+++ b/data/source/weekly/cs-en-us-078pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
         <v>3</v>
       </c>
       <c r="H16" s="14">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I16" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16" s="14">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L16" s="14">
-        <v>-62.5</v>
+        <v>-43.75</v>
       </c>
       <c r="M16" s="14">
-        <v>-70</v>
+        <v>-64</v>
       </c>
       <c r="N16" s="14">
-        <v>-95.488721804511</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -984,31 +984,31 @@
         <v>-20</v>
       </c>
       <c r="F17" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H17" s="14">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I17" s="15">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J17" s="15">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K17" s="14">
-        <v>-12.5</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="L17" s="14">
-        <v>-4.545454545454</v>
+        <v>4.166666666666</v>
       </c>
       <c r="M17" s="14">
-        <v>425</v>
+        <v>525</v>
       </c>
       <c r="N17" s="14">
-        <v>-16</v>
+        <v>-7.407407407407</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H18" s="14">
-        <v>-63.636363636363</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J18" s="15">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K18" s="14">
-        <v>-50</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="L18" s="14">
-        <v>-50</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="M18" s="14">
-        <v>-38.888888888888</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="N18" s="14">
-        <v>-90.677966101694</v>
+        <v>-89.682539682539</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,54 +1057,54 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" s="14">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G19" s="15">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H19" s="14">
-        <v>27.777777777777</v>
+        <v>-12.5</v>
       </c>
       <c r="I19" s="15">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J19" s="15">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="K19" s="14">
-        <v>-7.5</v>
+        <v>-16</v>
       </c>
       <c r="L19" s="14">
-        <v>-37.288135593220</v>
+        <v>-35.384615384615</v>
       </c>
       <c r="M19" s="14">
-        <v>-33.928571428571</v>
+        <v>-34.375</v>
       </c>
       <c r="N19" s="14">
-        <v>-35.087719298245</v>
+        <v>-35.384615384615</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="15">
         <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>5</v>
@@ -1119,19 +1119,19 @@
         <v>8</v>
       </c>
       <c r="J20" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14">
-        <v>-65.217391304347</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="M20" s="14">
-        <v>14.285714285714</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.628415300546</v>
+        <v>-96.153846153846</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.052631578947</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="F21" s="17">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G21" s="17">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-7.407407407407</v>
       </c>
       <c r="I21" s="17">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="J21" s="17">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.831683168316</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L21" s="18">
-        <v>-41.666666666666</v>
+        <v>-36.774193548387</v>
       </c>
       <c r="M21" s="18">
-        <v>-20</v>
+        <v>-20.967741935483</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.969465648855</v>
+        <v>-83.304940374787</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="I22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="15">
         <v>5</v>
       </c>
       <c r="K22" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="L22" s="14">
-        <v>66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="15">
+      <c r="C23" s="15">
         <v>1</v>
       </c>
-      <c r="E23" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="15">
+        <v>1</v>
       </c>
       <c r="G23" s="15">
         <v>1</v>
       </c>
       <c r="H23" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I23" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J23" s="15">
         <v>3</v>
       </c>
       <c r="K23" s="14">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L23" s="14">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="M23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D24" s="15">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E24" s="14">
-        <v>-53.125</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="G24" s="15">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="H24" s="14">
-        <v>-22.448979591836</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="I24" s="15">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="J24" s="15">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="K24" s="14">
-        <v>-13.227513227513</v>
+        <v>-16.431924882629</v>
       </c>
       <c r="L24" s="14">
-        <v>19.708029197080</v>
+        <v>14.102564102564</v>
       </c>
       <c r="M24" s="14">
-        <v>54.716981132075</v>
+        <v>45.901639344262</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D25" s="15">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E25" s="14">
-        <v>-82.758620689655</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="F25" s="15">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G25" s="15">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H25" s="14">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="15">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="J25" s="15">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="K25" s="14">
-        <v>-23.188405797101</v>
+        <v>-25.157232704402</v>
       </c>
       <c r="L25" s="14">
-        <v>26.190476190476</v>
+        <v>22.680412371134</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>6</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F26" s="15">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" s="15">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H26" s="14">
-        <v>187.5</v>
+        <v>100</v>
       </c>
       <c r="I26" s="15">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J26" s="15">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K26" s="14">
-        <v>-3.225806451612</v>
+        <v>0</v>
       </c>
       <c r="L26" s="14">
-        <v>25</v>
+        <v>16.129032258064</v>
       </c>
       <c r="M26" s="14">
-        <v>0</v>
+        <v>5.882352941176</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1412,7 +1412,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H28" s="14">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="I28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L28" s="14">
-        <v>-57.142857142857</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="15">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="15">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="15">
-        <v>1</v>
-      </c>
-      <c r="H31" s="14">
-        <v>-100</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-078pct.xlsx
+++ b/data/source/weekly/cs-en-us-078pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="15">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -904,43 +904,43 @@
       <c r="F15" s="15">
         <v>1</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
-        <v>0</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="15">
         <v>2</v>
       </c>
       <c r="K15" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N15" s="14">
-        <v>-85.714285714285</v>
+        <v>-71.428571428571</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>3</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
         <v>5</v>
@@ -955,19 +955,19 @@
         <v>9</v>
       </c>
       <c r="J16" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" s="14">
-        <v>28.571428571428</v>
+        <v>12.5</v>
       </c>
       <c r="L16" s="14">
-        <v>-43.75</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="14">
-        <v>-64</v>
+        <v>-65.384615384615</v>
       </c>
       <c r="N16" s="14">
-        <v>-94.117647058823</v>
+        <v>-94.444444444444</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>-20</v>
+        <v>200</v>
       </c>
       <c r="F17" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G17" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H17" s="14">
+        <v>7.692307692307</v>
+      </c>
+      <c r="I17" s="15">
+        <v>31</v>
+      </c>
+      <c r="J17" s="15">
+        <v>31</v>
+      </c>
+      <c r="K17" s="14">
         <v>0</v>
       </c>
-      <c r="I17" s="15">
-        <v>25</v>
-      </c>
-      <c r="J17" s="15">
-        <v>29</v>
-      </c>
-      <c r="K17" s="14">
-        <v>-13.793103448275</v>
-      </c>
       <c r="L17" s="14">
-        <v>4.166666666666</v>
+        <v>29.166666666666</v>
       </c>
       <c r="M17" s="14">
-        <v>525</v>
+        <v>287.5</v>
       </c>
       <c r="N17" s="14">
-        <v>-7.407407407407</v>
+        <v>6.896551724137</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
         <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H18" s="14">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="I18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K18" s="14">
-        <v>-43.478260869565</v>
+        <v>-44</v>
       </c>
       <c r="L18" s="14">
-        <v>-40.909090909090</v>
+        <v>-44</v>
       </c>
       <c r="M18" s="14">
-        <v>-40.909090909090</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="N18" s="14">
-        <v>-89.682539682539</v>
+        <v>-89.705882352941</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,78 +1060,78 @@
         <v>5</v>
       </c>
       <c r="D19" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>-50</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F19" s="15">
         <v>21</v>
       </c>
       <c r="G19" s="15">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H19" s="14">
-        <v>-12.5</v>
+        <v>-30</v>
       </c>
       <c r="I19" s="15">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J19" s="15">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K19" s="14">
-        <v>-16</v>
+        <v>-24.590163934426</v>
       </c>
       <c r="L19" s="14">
-        <v>-35.384615384615</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="M19" s="14">
-        <v>-34.375</v>
+        <v>-35.211267605633</v>
       </c>
       <c r="N19" s="14">
-        <v>-35.384615384615</v>
+        <v>-36.986301369863</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="15">
+      <c r="C20" s="15">
         <v>1</v>
       </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
+        <v>4</v>
+      </c>
+      <c r="G20" s="15">
         <v>5</v>
       </c>
-      <c r="G20" s="15">
-        <v>6</v>
-      </c>
       <c r="H20" s="14">
-        <v>-16.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J20" s="15">
         <v>8</v>
       </c>
       <c r="K20" s="14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="L20" s="14">
-        <v>-69.230769230769</v>
+        <v>-67.857142857142</v>
       </c>
       <c r="M20" s="14">
-        <v>-11.111111111111</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N20" s="14">
-        <v>-96.153846153846</v>
+        <v>-96.086956521739</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-22.222222222222</v>
+        <v>-18.75</v>
       </c>
       <c r="F21" s="17">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G21" s="17">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H21" s="18">
-        <v>-7.407407407407</v>
+        <v>-16.393442622950</v>
       </c>
       <c r="I21" s="17">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="J21" s="17">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.647058823529</v>
+        <v>-17.777777777777</v>
       </c>
       <c r="L21" s="18">
-        <v>-36.774193548387</v>
+        <v>-34.319526627218</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.967741935483</v>
+        <v>-22.377622377622</v>
       </c>
       <c r="N21" s="18">
-        <v>-83.304940374787</v>
+        <v>-82.629107981220</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>5</v>
-      </c>
-      <c r="G22" s="15">
-        <v>1</v>
-      </c>
-      <c r="H22" s="14">
-        <v>400</v>
+        <v>3</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="15">
         <v>6</v>
@@ -1207,7 +1207,7 @@
         <v>20</v>
       </c>
       <c r="L22" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M22" s="14">
         <v>-14.285714285714</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D24" s="15">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="E24" s="14">
-        <v>-41.666666666666</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="F24" s="15">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="G24" s="15">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H24" s="14">
-        <v>-38.095238095238</v>
+        <v>-29.203539823008</v>
       </c>
       <c r="I24" s="15">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="J24" s="15">
-        <v>213</v>
+        <v>244</v>
       </c>
       <c r="K24" s="14">
-        <v>-16.431924882629</v>
+        <v>-15.983606557377</v>
       </c>
       <c r="L24" s="14">
-        <v>14.102564102564</v>
+        <v>16.477272727272</v>
       </c>
       <c r="M24" s="14">
-        <v>45.901639344262</v>
+        <v>49.635036496350</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D25" s="15">
         <v>21</v>
       </c>
       <c r="E25" s="14">
-        <v>-38.095238095238</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="15">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G25" s="15">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="H25" s="14">
-        <v>-50</v>
+        <v>-47.252747252747</v>
       </c>
       <c r="I25" s="15">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="J25" s="15">
-        <v>159</v>
+        <v>180</v>
       </c>
       <c r="K25" s="14">
-        <v>-25.157232704402</v>
+        <v>-26.111111111111</v>
       </c>
       <c r="L25" s="14">
-        <v>22.680412371134</v>
+        <v>22.018348623853</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G26" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H26" s="14">
-        <v>100</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I26" s="15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J26" s="15">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K26" s="14">
         <v>0</v>
       </c>
       <c r="L26" s="14">
-        <v>16.129032258064</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M26" s="14">
-        <v>5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="15">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1396,23 +1396,23 @@
       <c r="F27" s="15">
         <v>1</v>
       </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
-      <c r="H27" s="14">
-        <v>-50</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="15">
         <v>3</v>
       </c>
       <c r="K27" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L27" s="14">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I28" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J28" s="15">
         <v>9</v>
       </c>
       <c r="K28" s="14">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L28" s="14">
-        <v>-58.823529411764</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,26 +1551,26 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>-100</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="14">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-078pct.xlsx
+++ b/data/source/weekly/cs-en-us-078pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -854,37 +854,37 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="14">
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
         <v>-100</v>
       </c>
+      <c r="L14" s="15">
+        <v>-100</v>
+      </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -892,213 +892,213 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>1</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="15">
+      <c r="J15" s="14">
         <v>2</v>
       </c>
-      <c r="J15" s="15">
-        <v>2</v>
-      </c>
-      <c r="K15" s="14">
+      <c r="K15" s="15">
+        <v>-50</v>
+      </c>
+      <c r="L15" s="15">
         <v>0</v>
       </c>
-      <c r="L15" s="14">
-        <v>100</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N15" s="14">
-        <v>-71.428571428571</v>
+      <c r="M15" s="15">
+        <v>-50</v>
+      </c>
+      <c r="N15" s="15">
+        <v>-87.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="15">
-        <v>1</v>
-      </c>
-      <c r="E16" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="15">
+      <c r="C16" s="14">
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
         <v>5</v>
       </c>
-      <c r="G16" s="15">
-        <v>3</v>
-      </c>
-      <c r="H16" s="14">
-        <v>66.666666666666</v>
-      </c>
-      <c r="I16" s="15">
-        <v>9</v>
-      </c>
-      <c r="J16" s="15">
+      <c r="E16" s="15">
+        <v>-60</v>
+      </c>
+      <c r="F16" s="14">
+        <v>7</v>
+      </c>
+      <c r="G16" s="14">
         <v>8</v>
       </c>
-      <c r="K16" s="14">
-        <v>12.5</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-50</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-65.384615384615</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-94.444444444444</v>
+      <c r="H16" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="I16" s="14">
+        <v>11</v>
+      </c>
+      <c r="J16" s="14">
+        <v>13</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-15.384615384615</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-45</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-59.259259259259</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-93.641618497109</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>6</v>
-      </c>
-      <c r="D17" s="15">
-        <v>2</v>
-      </c>
-      <c r="E17" s="14">
-        <v>200</v>
-      </c>
-      <c r="F17" s="15">
-        <v>14</v>
-      </c>
-      <c r="G17" s="15">
-        <v>13</v>
-      </c>
-      <c r="H17" s="14">
-        <v>7.692307692307</v>
-      </c>
-      <c r="I17" s="15">
-        <v>31</v>
-      </c>
-      <c r="J17" s="15">
-        <v>31</v>
-      </c>
-      <c r="K17" s="14">
-        <v>0</v>
-      </c>
-      <c r="L17" s="14">
-        <v>29.166666666666</v>
-      </c>
-      <c r="M17" s="14">
-        <v>287.5</v>
-      </c>
-      <c r="N17" s="14">
-        <v>6.896551724137</v>
+      <c r="C17" s="14">
+        <v>7</v>
+      </c>
+      <c r="D17" s="14">
+        <v>5</v>
+      </c>
+      <c r="E17" s="15">
+        <v>40</v>
+      </c>
+      <c r="F17" s="14">
+        <v>21</v>
+      </c>
+      <c r="G17" s="14">
+        <v>17</v>
+      </c>
+      <c r="H17" s="15">
+        <v>23.529411764705</v>
+      </c>
+      <c r="I17" s="14">
+        <v>39</v>
+      </c>
+      <c r="J17" s="14">
+        <v>36</v>
+      </c>
+      <c r="K17" s="15">
+        <v>8.333333333333</v>
+      </c>
+      <c r="L17" s="15">
+        <v>34.482758620689</v>
+      </c>
+      <c r="M17" s="15">
+        <v>387.5</v>
+      </c>
+      <c r="N17" s="15">
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="15">
-        <v>2</v>
-      </c>
-      <c r="E18" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F18" s="15">
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
+      </c>
+      <c r="F18" s="14">
         <v>6</v>
       </c>
-      <c r="G18" s="15">
-        <v>10</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-40</v>
-      </c>
-      <c r="I18" s="15">
-        <v>14</v>
-      </c>
-      <c r="J18" s="15">
-        <v>25</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-44</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-44</v>
-      </c>
-      <c r="M18" s="14">
-        <v>-48.148148148148</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-89.705882352941</v>
+      <c r="G18" s="14">
+        <v>8</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-25</v>
+      </c>
+      <c r="I18" s="14">
+        <v>16</v>
+      </c>
+      <c r="J18" s="14">
+        <v>26</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-38.461538461538</v>
+      </c>
+      <c r="L18" s="15">
+        <v>-38.461538461538</v>
+      </c>
+      <c r="M18" s="15">
+        <v>-46.666666666666</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-89.041095890411</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>5</v>
-      </c>
-      <c r="D19" s="15">
-        <v>11</v>
-      </c>
-      <c r="E19" s="14">
-        <v>-54.545454545454</v>
-      </c>
-      <c r="F19" s="15">
-        <v>21</v>
-      </c>
-      <c r="G19" s="15">
-        <v>30</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-30</v>
-      </c>
-      <c r="I19" s="15">
-        <v>46</v>
-      </c>
-      <c r="J19" s="15">
-        <v>61</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-24.590163934426</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-36.111111111111</v>
-      </c>
-      <c r="M19" s="14">
-        <v>-35.211267605633</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-36.986301369863</v>
+      <c r="C19" s="14">
+        <v>6</v>
+      </c>
+      <c r="D19" s="14">
+        <v>10</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-40</v>
+      </c>
+      <c r="F19" s="14">
+        <v>21</v>
+      </c>
+      <c r="G19" s="14">
+        <v>39</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-46.153846153846</v>
+      </c>
+      <c r="I19" s="14">
+        <v>52</v>
+      </c>
+      <c r="J19" s="14">
+        <v>71</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-26.760563380281</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-35.802469135802</v>
+      </c>
+      <c r="M19" s="15">
+        <v>-35.802469135802</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-34.177215189873</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>1</v>
+      <c r="C20" s="14">
+        <v>2</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1106,32 +1106,32 @@
       <c r="E20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="14">
         <v>4</v>
       </c>
-      <c r="G20" s="15">
-        <v>5</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-20</v>
-      </c>
-      <c r="I20" s="15">
-        <v>9</v>
-      </c>
-      <c r="J20" s="15">
+      <c r="G20" s="14">
+        <v>2</v>
+      </c>
+      <c r="H20" s="15">
+        <v>100</v>
+      </c>
+      <c r="I20" s="14">
+        <v>11</v>
+      </c>
+      <c r="J20" s="14">
         <v>8</v>
       </c>
-      <c r="K20" s="14">
-        <v>12.5</v>
-      </c>
-      <c r="L20" s="14">
-        <v>-67.857142857142</v>
-      </c>
-      <c r="M20" s="14">
-        <v>-18.181818181818</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-96.086956521739</v>
+      <c r="K20" s="15">
+        <v>37.5</v>
+      </c>
+      <c r="L20" s="15">
+        <v>-63.333333333333</v>
+      </c>
+      <c r="M20" s="15">
+        <v>-21.428571428571</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-95.473251028806</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.75</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="F21" s="17">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="G21" s="17">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.393442622950</v>
+        <v>-21.333333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="J21" s="17">
-        <v>135</v>
+        <v>157</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.777777777777</v>
+        <v>-17.197452229299</v>
       </c>
       <c r="L21" s="18">
-        <v>-34.319526627218</v>
+        <v>-30.851063829787</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.377622377622</v>
+        <v>-19.753086419753</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.629107981220</v>
+        <v>-80.910425844346</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,8 +1188,8 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="15">
-        <v>3</v>
+      <c r="F22" s="14">
+        <v>2</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1197,20 +1197,20 @@
       <c r="H22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I22" s="15">
-        <v>6</v>
-      </c>
-      <c r="J22" s="15">
+      <c r="I22" s="14">
+        <v>7</v>
+      </c>
+      <c r="J22" s="14">
         <v>5</v>
       </c>
-      <c r="K22" s="14">
-        <v>20</v>
-      </c>
-      <c r="L22" s="14">
-        <v>50</v>
-      </c>
-      <c r="M22" s="14">
-        <v>-14.285714285714</v>
+      <c r="K22" s="15">
+        <v>40</v>
+      </c>
+      <c r="L22" s="15">
+        <v>40</v>
+      </c>
+      <c r="M22" s="15">
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1229,25 +1229,25 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="14">
         <v>1</v>
       </c>
-      <c r="G23" s="15">
+      <c r="G23" s="14">
         <v>1</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H23" s="15">
         <v>0</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="14">
         <v>2</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="14">
         <v>3</v>
       </c>
-      <c r="K23" s="14">
+      <c r="K23" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="L23" s="14">
+      <c r="L23" s="15">
         <v>-60</v>
       </c>
       <c r="M23" s="13" t="s">
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>27</v>
-      </c>
-      <c r="D24" s="15">
-        <v>31</v>
-      </c>
-      <c r="E24" s="14">
-        <v>-12.903225806451</v>
-      </c>
-      <c r="F24" s="15">
-        <v>80</v>
-      </c>
-      <c r="G24" s="15">
-        <v>113</v>
-      </c>
-      <c r="H24" s="14">
-        <v>-29.203539823008</v>
-      </c>
-      <c r="I24" s="15">
-        <v>205</v>
-      </c>
-      <c r="J24" s="15">
-        <v>244</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-15.983606557377</v>
-      </c>
-      <c r="L24" s="14">
-        <v>16.477272727272</v>
-      </c>
-      <c r="M24" s="14">
-        <v>49.635036496350</v>
+      <c r="C24" s="14">
+        <v>11</v>
+      </c>
+      <c r="D24" s="14">
+        <v>20</v>
+      </c>
+      <c r="E24" s="15">
+        <v>-45</v>
+      </c>
+      <c r="F24" s="14">
+        <v>66</v>
+      </c>
+      <c r="G24" s="14">
+        <v>107</v>
+      </c>
+      <c r="H24" s="15">
+        <v>-38.317757009345</v>
+      </c>
+      <c r="I24" s="14">
+        <v>215</v>
+      </c>
+      <c r="J24" s="14">
+        <v>264</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-18.560606060606</v>
+      </c>
+      <c r="L24" s="15">
+        <v>10.256410256410</v>
+      </c>
+      <c r="M24" s="15">
+        <v>43.333333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>14</v>
-      </c>
-      <c r="D25" s="15">
-        <v>21</v>
-      </c>
-      <c r="E25" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F25" s="15">
-        <v>48</v>
-      </c>
-      <c r="G25" s="15">
-        <v>91</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-47.252747252747</v>
-      </c>
-      <c r="I25" s="15">
-        <v>133</v>
-      </c>
-      <c r="J25" s="15">
-        <v>180</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-26.111111111111</v>
-      </c>
-      <c r="L25" s="14">
-        <v>22.018348623853</v>
+      <c r="C25" s="14">
+        <v>6</v>
+      </c>
+      <c r="D25" s="14">
+        <v>15</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-60</v>
+      </c>
+      <c r="F25" s="14">
+        <v>37</v>
+      </c>
+      <c r="G25" s="14">
+        <v>86</v>
+      </c>
+      <c r="H25" s="15">
+        <v>-56.976744186046</v>
+      </c>
+      <c r="I25" s="14">
+        <v>138</v>
+      </c>
+      <c r="J25" s="14">
+        <v>195</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-29.230769230769</v>
+      </c>
+      <c r="L25" s="15">
+        <v>15</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>3</v>
-      </c>
-      <c r="D26" s="15">
-        <v>2</v>
-      </c>
-      <c r="E26" s="14">
-        <v>50</v>
-      </c>
-      <c r="F26" s="15">
-        <v>16</v>
-      </c>
-      <c r="G26" s="15">
-        <v>13</v>
-      </c>
-      <c r="H26" s="14">
-        <v>23.076923076923</v>
-      </c>
-      <c r="I26" s="15">
-        <v>38</v>
-      </c>
-      <c r="J26" s="15">
-        <v>38</v>
-      </c>
-      <c r="K26" s="14">
-        <v>0</v>
-      </c>
-      <c r="L26" s="14">
-        <v>11.764705882352</v>
-      </c>
-      <c r="M26" s="14">
-        <v>0</v>
+      <c r="C26" s="14">
+        <v>5</v>
+      </c>
+      <c r="D26" s="14">
+        <v>8</v>
+      </c>
+      <c r="E26" s="15">
+        <v>-37.5</v>
+      </c>
+      <c r="F26" s="14">
+        <v>20</v>
+      </c>
+      <c r="G26" s="14">
+        <v>19</v>
+      </c>
+      <c r="H26" s="15">
+        <v>5.263157894736</v>
+      </c>
+      <c r="I26" s="14">
+        <v>43</v>
+      </c>
+      <c r="J26" s="14">
+        <v>46</v>
+      </c>
+      <c r="K26" s="15">
+        <v>-6.521739130434</v>
+      </c>
+      <c r="L26" s="15">
+        <v>16.216216216216</v>
+      </c>
+      <c r="M26" s="15">
+        <v>4.878048780487</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,8 +1393,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="15">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1402,17 +1402,17 @@
       <c r="H27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="14">
+        <v>2</v>
+      </c>
+      <c r="J27" s="14">
         <v>3</v>
       </c>
-      <c r="J27" s="15">
-        <v>3</v>
-      </c>
-      <c r="K27" s="14">
-        <v>0</v>
-      </c>
-      <c r="L27" s="14">
-        <v>0</v>
+      <c r="K27" s="15">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="L27" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="14">
+        <v>4</v>
+      </c>
+      <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="G28" s="15">
-        <v>2</v>
-      </c>
-      <c r="H28" s="14">
-        <v>50</v>
-      </c>
-      <c r="I28" s="15">
-        <v>8</v>
-      </c>
-      <c r="J28" s="15">
+      <c r="H28" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="I28" s="14">
         <v>9</v>
       </c>
-      <c r="K28" s="14">
-        <v>-11.111111111111</v>
-      </c>
-      <c r="L28" s="14">
-        <v>-57.894736842105</v>
+      <c r="J28" s="14">
+        <v>11</v>
+      </c>
+      <c r="K28" s="15">
+        <v>-18.181818181818</v>
+      </c>
+      <c r="L28" s="15">
+        <v>-55</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1484,7 +1484,7 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I29" s="14">
         <v>1</v>
       </c>
       <c r="J29" s="13" t="s">
@@ -1493,13 +1493,13 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="14">
+      <c r="L29" s="15">
         <v>0</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N29" s="14">
+      <c r="N29" s="15">
         <v>-50</v>
       </c>
     </row>
@@ -1525,7 +1525,7 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I30" s="14">
         <v>1</v>
       </c>
       <c r="J30" s="13" t="s">
@@ -1534,13 +1534,13 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="14">
+      <c r="L30" s="15">
         <v>0</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="N30" s="14">
+      <c r="N30" s="15">
         <v>-50</v>
       </c>
     </row>
@@ -1548,32 +1548,32 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D31" s="15">
+      <c r="C31" s="14">
         <v>1</v>
       </c>
-      <c r="E31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="15">
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="H31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="15">
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
+      </c>
+      <c r="I31" s="14">
+        <v>1</v>
+      </c>
+      <c r="J31" s="14">
         <v>2</v>
       </c>
-      <c r="K31" s="14">
-        <v>-100</v>
+      <c r="K31" s="15">
+        <v>-50</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>5</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>7</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>1</v>
       </c>
-      <c r="I39" s="15">
+      <c r="I39" s="14">
         <v>1</v>
       </c>
-      <c r="J39" s="15">
+      <c r="J39" s="14">
         <v>2</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>100</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>100</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-71.428571428571</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-60</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>12</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>26</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>12</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>11</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>13</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>18.181818181818</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>8.333333333333</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-50</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>8.333333333333</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>1115</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>865</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>464</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>251</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>78</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-68.924302788844</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-83.189655172413</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-90.982658959537</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-93.004484304932</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>251</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>268</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>158</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>108</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>159</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>47.222222222222</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>0.632911392405</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-40.671641791044</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-36.653386454183</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>1644</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>797</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>498</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>344</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>119</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-65.406976744186</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-76.104417670682</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-85.069008782936</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-92.761557177615</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>550</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>510</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>452</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>369</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>407</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>10.298102981029</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>-9.955752212389</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-20.196078431372</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-26</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>1596</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>1034</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>370</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>244</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>70</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-71.311475409836</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-81.081081081081</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-93.230174081237</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-95.614035087719</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-078pct.xlsx
+++ b/data/source/weekly/cs-en-us-078pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F16" s="14">
         <v>5</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-60</v>
-      </c>
-      <c r="F16" s="14">
-        <v>7</v>
       </c>
       <c r="G16" s="14">
         <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-12.5</v>
+        <v>-37.5</v>
       </c>
       <c r="I16" s="14">
         <v>11</v>
       </c>
       <c r="J16" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K16" s="15">
-        <v>-15.384615384615</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L16" s="15">
-        <v>-45</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-59.259259259259</v>
+        <v>-60.714285714285</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.641618497109</v>
+        <v>-94.148936170212</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
-      </c>
-      <c r="D17" s="14">
         <v>5</v>
       </c>
-      <c r="E17" s="15">
-        <v>40</v>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>23.529411764705</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J17" s="14">
         <v>36</v>
       </c>
       <c r="K17" s="15">
-        <v>8.333333333333</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L17" s="15">
-        <v>34.482758620689</v>
+        <v>29.411764705882</v>
       </c>
       <c r="M17" s="15">
-        <v>387.5</v>
+        <v>450</v>
       </c>
       <c r="N17" s="15">
-        <v>30</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J18" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K18" s="15">
-        <v>-38.461538461538</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="L18" s="15">
-        <v>-38.461538461538</v>
+        <v>-41.379310344827</v>
       </c>
       <c r="M18" s="15">
-        <v>-46.666666666666</v>
+        <v>-51.428571428571</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.041095890411</v>
+        <v>-89.240506329113</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>-40</v>
+        <v>40</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="H19" s="15">
-        <v>-46.153846153846</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="I19" s="14">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J19" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="K19" s="15">
-        <v>-26.760563380281</v>
+        <v>-22.368421052631</v>
       </c>
       <c r="L19" s="15">
-        <v>-35.802469135802</v>
+        <v>-32.954545454545</v>
       </c>
       <c r="M19" s="15">
-        <v>-35.802469135802</v>
+        <v>-37.234042553191</v>
       </c>
       <c r="N19" s="15">
-        <v>-34.177215189873</v>
+        <v>-31.395348837209</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="15">
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
         <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K20" s="15">
-        <v>37.5</v>
+        <v>20</v>
       </c>
       <c r="L20" s="15">
-        <v>-63.333333333333</v>
+        <v>-60</v>
       </c>
       <c r="M20" s="15">
-        <v>-21.428571428571</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.473251028806</v>
+        <v>-95.419847328244</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="E21" s="18">
-        <v>-18.181818181818</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F21" s="17">
         <v>59</v>
       </c>
       <c r="G21" s="17">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.333333333333</v>
+        <v>-9.230769230769</v>
       </c>
       <c r="I21" s="17">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="J21" s="17">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.197452229299</v>
+        <v>-13.253012048192</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.851063829787</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.753086419753</v>
+        <v>-21.311475409836</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.910425844346</v>
+        <v>-80.434782608695</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1207,7 +1207,7 @@
         <v>40</v>
       </c>
       <c r="L22" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M22" s="15">
         <v>0</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>1</v>
-      </c>
-      <c r="G23" s="14">
-        <v>1</v>
-      </c>
-      <c r="H23" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J23" s="14">
         <v>3</v>
       </c>
       <c r="K23" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-60</v>
-      </c>
-      <c r="M23" s="13" t="s">
-        <v>21</v>
+        <v>-40</v>
+      </c>
+      <c r="M23" s="15">
+        <v>50</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D24" s="14">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>-45</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F24" s="14">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G24" s="14">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="H24" s="15">
-        <v>-38.317757009345</v>
+        <v>-30.097087378640</v>
       </c>
       <c r="I24" s="14">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="J24" s="14">
-        <v>264</v>
+        <v>292</v>
       </c>
       <c r="K24" s="15">
-        <v>-18.560606060606</v>
+        <v>-19.520547945205</v>
       </c>
       <c r="L24" s="15">
-        <v>10.256410256410</v>
+        <v>6.334841628959</v>
       </c>
       <c r="M24" s="15">
-        <v>43.333333333333</v>
+        <v>38.235294117647</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E25" s="15">
-        <v>-60</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="F25" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G25" s="14">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="H25" s="15">
-        <v>-56.976744186046</v>
+        <v>-46.052631578947</v>
       </c>
       <c r="I25" s="14">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="J25" s="14">
-        <v>195</v>
+        <v>214</v>
       </c>
       <c r="K25" s="15">
-        <v>-29.230769230769</v>
+        <v>-31.308411214953</v>
       </c>
       <c r="L25" s="15">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-37.5</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G26" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H26" s="15">
-        <v>5.263157894736</v>
+        <v>-19.047619047619</v>
       </c>
       <c r="I26" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J26" s="14">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="K26" s="15">
-        <v>-6.521739130434</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="L26" s="15">
-        <v>16.216216216216</v>
+        <v>6.976744186046</v>
       </c>
       <c r="M26" s="15">
-        <v>4.878048780487</v>
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
@@ -1444,16 +1444,16 @@
         <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="14">
         <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-18.181818181818</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L28" s="15">
-        <v>-55</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,7 +1485,7 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1494,21 +1494,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
+        <v>100</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N29" s="15">
         <v>0</v>
-      </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N29" s="15">
-        <v>-50</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,7 +1526,7 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1535,21 +1535,21 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
+        <v>100</v>
+      </c>
+      <c r="M30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="N30" s="15">
         <v>0</v>
-      </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="N30" s="15">
-        <v>-50</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="14">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-078pct.xlsx
+++ b/data/source/weekly/cs-en-us-078pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -920,7 +920,7 @@
         <v>-50</v>
       </c>
       <c r="L15" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="M15" s="15">
         <v>-50</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-37.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K16" s="15">
-        <v>-21.428571428571</v>
+        <v>-25</v>
       </c>
       <c r="L16" s="15">
-        <v>-54.166666666666</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="15">
-        <v>-60.714285714285</v>
+        <v>-60</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.148936170212</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
+        <v>2</v>
+      </c>
+      <c r="E17" s="15">
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H17" s="15">
-        <v>83.333333333333</v>
+        <v>122.222222222222</v>
       </c>
       <c r="I17" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="J17" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K17" s="15">
-        <v>22.222222222222</v>
+        <v>21.052631578947</v>
       </c>
       <c r="L17" s="15">
-        <v>29.411764705882</v>
+        <v>31.428571428571</v>
       </c>
       <c r="M17" s="15">
-        <v>450</v>
+        <v>475</v>
       </c>
       <c r="N17" s="15">
-        <v>37.5</v>
+        <v>21.052631578947</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="14">
         <v>17</v>
       </c>
       <c r="J18" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K18" s="15">
-        <v>-37.037037037037</v>
+        <v>-41.379310344827</v>
       </c>
       <c r="L18" s="15">
         <v>-41.379310344827</v>
       </c>
       <c r="M18" s="15">
-        <v>-51.428571428571</v>
+        <v>-55.263157894736</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.240506329113</v>
+        <v>-89.940828402366</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>40</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H19" s="15">
-        <v>-36.111111111111</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="I19" s="14">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J19" s="14">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="K19" s="15">
-        <v>-22.368421052631</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="L19" s="15">
-        <v>-32.954545454545</v>
+        <v>-31.182795698924</v>
       </c>
       <c r="M19" s="15">
-        <v>-37.234042553191</v>
+        <v>-35.353535353535</v>
       </c>
       <c r="N19" s="15">
-        <v>-31.395348837209</v>
+        <v>-37.254901960784</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="E20" s="15">
-        <v>-50</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H20" s="15">
-        <v>33.333333333333</v>
+        <v>200</v>
       </c>
       <c r="I20" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J20" s="14">
         <v>10</v>
       </c>
       <c r="K20" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="L20" s="15">
-        <v>-60</v>
+        <v>-56.25</v>
       </c>
       <c r="M20" s="15">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.419847328244</v>
+        <v>-95.017793594306</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>9</v>
+      </c>
+      <c r="D21" s="17">
         <v>14</v>
       </c>
-      <c r="D21" s="17">
-        <v>9</v>
-      </c>
       <c r="E21" s="18">
-        <v>55.555555555555</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="F21" s="17">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="G21" s="17">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="H21" s="18">
-        <v>-9.230769230769</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="I21" s="17">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="J21" s="17">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.253012048192</v>
+        <v>-14.444444444444</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.769230769230</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.311475409836</v>
+        <v>-21.025641025641</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.434782608695</v>
+        <v>-80.845771144278</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
+        <v>1</v>
+      </c>
+      <c r="G22" s="14">
         <v>2</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="H22" s="15">
+        <v>-50</v>
       </c>
       <c r="I22" s="14">
         <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,17 +1220,17 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="14">
         <v>1</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F23" s="14">
-        <v>2</v>
       </c>
       <c r="G23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E24" s="15">
-        <v>-28.571428571428</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F24" s="14">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G24" s="14">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="H24" s="15">
-        <v>-30.097087378640</v>
+        <v>-33.035714285714</v>
       </c>
       <c r="I24" s="14">
-        <v>235</v>
+        <v>252</v>
       </c>
       <c r="J24" s="14">
-        <v>292</v>
+        <v>325</v>
       </c>
       <c r="K24" s="15">
-        <v>-19.520547945205</v>
+        <v>-22.461538461538</v>
       </c>
       <c r="L24" s="15">
-        <v>6.334841628959</v>
+        <v>5</v>
       </c>
       <c r="M24" s="15">
-        <v>38.235294117647</v>
+        <v>39.226519337016</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E25" s="15">
-        <v>-52.631578947368</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="F25" s="14">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G25" s="14">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H25" s="15">
-        <v>-46.052631578947</v>
+        <v>-45.833333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="J25" s="14">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="K25" s="15">
-        <v>-31.308411214953</v>
+        <v>-31.601731601731</v>
       </c>
       <c r="L25" s="15">
-        <v>5</v>
+        <v>3.267973856209</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
         <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="G26" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H26" s="15">
-        <v>-19.047619047619</v>
+        <v>-4.545454545454</v>
       </c>
       <c r="I26" s="14">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="J26" s="14">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.538461538461</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="L26" s="15">
-        <v>6.976744186046</v>
+        <v>24.444444444444</v>
       </c>
       <c r="M26" s="15">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1412,7 +1412,7 @@
         <v>-33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
         <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-9.090909090909</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L28" s="15">
-        <v>-54.545454545454</v>
+        <v>-59.090909090909</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1494,21 +1494,21 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-078pct.xlsx
+++ b/data/source/weekly/cs-en-us-078pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
       </c>
       <c r="I15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="M15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-87.5</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
+        <v>0</v>
+      </c>
+      <c r="F16" s="14">
+        <v>5</v>
+      </c>
+      <c r="G16" s="14">
+        <v>10</v>
+      </c>
+      <c r="H16" s="15">
         <v>-50</v>
       </c>
-      <c r="F16" s="14">
-        <v>3</v>
-      </c>
-      <c r="G16" s="14">
-        <v>9</v>
-      </c>
-      <c r="H16" s="15">
-        <v>-66.666666666666</v>
-      </c>
       <c r="I16" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J16" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K16" s="15">
-        <v>-25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L16" s="15">
-        <v>-50</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="M16" s="15">
-        <v>-60</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.117647058823</v>
+        <v>-93.457943925233</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,13 +975,13 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
         <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F17" s="14">
         <v>20</v>
@@ -993,63 +993,63 @@
         <v>122.222222222222</v>
       </c>
       <c r="I17" s="14">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="J17" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K17" s="15">
-        <v>21.052631578947</v>
+        <v>30</v>
       </c>
       <c r="L17" s="15">
-        <v>31.428571428571</v>
+        <v>30</v>
       </c>
       <c r="M17" s="15">
-        <v>475</v>
+        <v>477.777777777778</v>
       </c>
       <c r="N17" s="15">
-        <v>21.052631578947</v>
+        <v>26.829268292682</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>-66.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="I18" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J18" s="14">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K18" s="15">
-        <v>-41.379310344827</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-41.379310344827</v>
+        <v>-47.222222222222</v>
       </c>
       <c r="M18" s="15">
-        <v>-55.263157894736</v>
+        <v>-54.761904761904</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.940828402366</v>
+        <v>-89.502762430939</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,10 +1057,10 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
         <v>-50</v>
@@ -1069,28 +1069,28 @@
         <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H19" s="15">
-        <v>-35.294117647058</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J19" s="14">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="K19" s="15">
-        <v>-23.809523809523</v>
+        <v>-26.595744680851</v>
       </c>
       <c r="L19" s="15">
-        <v>-31.182795698924</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="M19" s="15">
-        <v>-35.353535353535</v>
+        <v>-34.905660377358</v>
       </c>
       <c r="N19" s="15">
-        <v>-37.254901960784</v>
+        <v>-38.392857142857</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J20" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K20" s="15">
-        <v>40</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L20" s="15">
-        <v>-56.25</v>
+        <v>-59.459459459459</v>
       </c>
       <c r="M20" s="15">
-        <v>-22.222222222222</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="15">
-        <v>-95.017793594306</v>
+        <v>-94.897959183673</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>-35.714285714285</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="G21" s="17">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="H21" s="18">
-        <v>-13.114754098360</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="I21" s="17">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="J21" s="17">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.444444444444</v>
+        <v>-13.197969543147</v>
       </c>
       <c r="L21" s="18">
-        <v>-29.032258064516</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="M21" s="18">
-        <v>-21.025641025641</v>
+        <v>-19.718309859154</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.845771144278</v>
+        <v>-79.929577464788</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1188,26 +1188,26 @@
       <c r="E22" s="15">
         <v>-100</v>
       </c>
-      <c r="F22" s="14">
-        <v>1</v>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L22" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="M22" s="15">
         <v>-12.5</v>
@@ -1248,7 +1248,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="M23" s="15">
         <v>50</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-45.454545454545</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="F24" s="14">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="G24" s="14">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H24" s="15">
-        <v>-33.035714285714</v>
+        <v>-43.925233644859</v>
       </c>
       <c r="I24" s="14">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="J24" s="14">
-        <v>325</v>
+        <v>351</v>
       </c>
       <c r="K24" s="15">
-        <v>-22.461538461538</v>
+        <v>-24.786324786324</v>
       </c>
       <c r="L24" s="15">
-        <v>5</v>
+        <v>-0.751879699248</v>
       </c>
       <c r="M24" s="15">
-        <v>39.226519337016</v>
+        <v>35.384615384615</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E25" s="15">
-        <v>-35.294117647058</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G25" s="14">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H25" s="15">
-        <v>-45.833333333333</v>
+        <v>-53.030303030303</v>
       </c>
       <c r="I25" s="14">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J25" s="14">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="K25" s="15">
-        <v>-31.601731601731</v>
+        <v>-33.739837398374</v>
       </c>
       <c r="L25" s="15">
-        <v>3.267973856209</v>
+        <v>-6.321839080459</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>66.666666666666</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G26" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H26" s="15">
-        <v>-4.545454545454</v>
+        <v>13.043478260869</v>
       </c>
       <c r="I26" s="14">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="J26" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.448275862068</v>
+        <v>4.918032786885</v>
       </c>
       <c r="L26" s="15">
-        <v>24.444444444444</v>
+        <v>25.490196078431</v>
       </c>
       <c r="M26" s="15">
-        <v>12</v>
+        <v>16.363636363636</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F27" s="14">
+        <v>1</v>
+      </c>
+      <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="L27" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="14">
         <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-18.181818181818</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L28" s="15">
-        <v>-59.090909090909</v>
+        <v>-56.521739130434</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1560,11 +1560,11 @@
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="14">
-        <v>1</v>
-      </c>
-      <c r="H31" s="15">
-        <v>0</v>
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>

--- a/data/source/weekly/cs-en-us-078pct.xlsx
+++ b/data/source/weekly/cs-en-us-078pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -892,14 +892,14 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I16" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J16" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>-22.222222222222</v>
+        <v>-15</v>
       </c>
       <c r="L16" s="15">
-        <v>-48.148148148148</v>
+        <v>-41.379310344827</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.823529411764</v>
+        <v>-54.054054054054</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.457943925233</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>1</v>
+      </c>
+      <c r="D17" s="14">
         <v>6</v>
       </c>
-      <c r="D17" s="14">
-        <v>2</v>
-      </c>
       <c r="E17" s="15">
-        <v>200</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H17" s="15">
-        <v>122.222222222222</v>
+        <v>40</v>
       </c>
       <c r="I17" s="14">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J17" s="14">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="K17" s="15">
-        <v>30</v>
+        <v>15.217391304347</v>
       </c>
       <c r="L17" s="15">
-        <v>30</v>
+        <v>29.268292682926</v>
       </c>
       <c r="M17" s="15">
-        <v>477.777777777778</v>
+        <v>488.888888888889</v>
       </c>
       <c r="N17" s="15">
-        <v>26.829268292682</v>
+        <v>12.765957446808</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J18" s="14">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K18" s="15">
-        <v>-36.666666666666</v>
+        <v>-34.375</v>
       </c>
       <c r="L18" s="15">
-        <v>-47.222222222222</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="M18" s="15">
-        <v>-54.761904761904</v>
+        <v>-55.319148936170</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.502762430939</v>
+        <v>-88.947368421052</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>-73.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>-33.333333333333</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="I19" s="14">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J19" s="14">
-        <v>94</v>
+        <v>109</v>
       </c>
       <c r="K19" s="15">
-        <v>-26.595744680851</v>
+        <v>-33.027522935779</v>
       </c>
       <c r="L19" s="15">
-        <v>-30.303030303030</v>
+        <v>-37.606837606837</v>
       </c>
       <c r="M19" s="15">
-        <v>-34.905660377358</v>
+        <v>-35.964912280701</v>
       </c>
       <c r="N19" s="15">
-        <v>-38.392857142857</v>
+        <v>-38.135593220339</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,13 +1098,13 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
         <v>6</v>
@@ -1116,22 +1116,22 @@
         <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J20" s="14">
         <v>11</v>
       </c>
       <c r="K20" s="15">
-        <v>36.363636363636</v>
+        <v>54.545454545454</v>
       </c>
       <c r="L20" s="15">
-        <v>-59.459459459459</v>
+        <v>-56.410256410256</v>
       </c>
       <c r="M20" s="15">
-        <v>-25</v>
+        <v>-15</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.897959183673</v>
+        <v>-94.603174603174</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>-52</v>
       </c>
       <c r="F21" s="17">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G21" s="17">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.451612903225</v>
+        <v>-20</v>
       </c>
       <c r="I21" s="17">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="J21" s="17">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.197969543147</v>
+        <v>-17.567567567567</v>
       </c>
       <c r="L21" s="18">
-        <v>-29.629629629629</v>
+        <v>-31.970260223048</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.718309859154</v>
+        <v>-20.087336244541</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.929577464788</v>
+        <v>-79.689234184239</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,7 +1183,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,13 +1201,13 @@
         <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K22" s="15">
+        <v>-30</v>
+      </c>
+      <c r="L22" s="15">
         <v>-22.222222222222</v>
-      </c>
-      <c r="L22" s="15">
-        <v>-12.5</v>
       </c>
       <c r="M22" s="15">
         <v>-12.5</v>
@@ -1223,29 +1223,29 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>3</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>1</v>
       </c>
-      <c r="G23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>21</v>
+      <c r="G23" s="14">
+        <v>3</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="I23" s="14">
         <v>3</v>
       </c>
       <c r="J23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K23" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="L23" s="15">
         <v>-50</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-53.846153846153</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G24" s="14">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H24" s="15">
-        <v>-43.925233644859</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="I24" s="14">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="J24" s="14">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="K24" s="15">
-        <v>-24.786324786324</v>
+        <v>-24.119241192411</v>
       </c>
       <c r="L24" s="15">
-        <v>-0.751879699248</v>
+        <v>-2.097902097902</v>
       </c>
       <c r="M24" s="15">
-        <v>35.384615384615</v>
+        <v>31.455399061032</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D25" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="F25" s="14">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G25" s="14">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H25" s="15">
-        <v>-53.030303030303</v>
+        <v>-47.692307692307</v>
       </c>
       <c r="I25" s="14">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="J25" s="14">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.739837398374</v>
+        <v>-33.846153846153</v>
       </c>
       <c r="L25" s="15">
-        <v>-6.321839080459</v>
+        <v>-11.340206185567</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D26" s="14">
         <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>166.666666666667</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="G26" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H26" s="15">
-        <v>13.043478260869</v>
+        <v>27.777777777777</v>
       </c>
       <c r="I26" s="14">
+        <v>66</v>
+      </c>
+      <c r="J26" s="14">
         <v>64</v>
       </c>
-      <c r="J26" s="14">
-        <v>61</v>
-      </c>
       <c r="K26" s="15">
-        <v>4.918032786885</v>
+        <v>3.125</v>
       </c>
       <c r="L26" s="15">
-        <v>25.490196078431</v>
+        <v>15.789473684210</v>
       </c>
       <c r="M26" s="15">
-        <v>16.363636363636</v>
+        <v>11.864406779661</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,14 +1384,14 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>-40</v>
       </c>
       <c r="L27" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="14">
-        <v>2</v>
-      </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
-      <c r="H28" s="15">
-        <v>0</v>
+      <c r="G28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
         <v>11</v>
       </c>
       <c r="K28" s="15">
-        <v>-9.090909090909</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L28" s="15">
-        <v>-56.521739130434</v>
+        <v>-62.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1494,13 +1494,13 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N29" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1535,13 +1535,13 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="N30" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="14">
-        <v>1</v>
+      <c r="F31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-078pct.xlsx
+++ b/data/source/weekly/cs-en-us-078pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -934,37 +934,37 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-14.285714285714</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K16" s="15">
-        <v>-15</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L16" s="15">
-        <v>-41.379310344827</v>
+        <v>-40</v>
       </c>
       <c r="M16" s="15">
-        <v>-54.054054054054</v>
+        <v>-56.097560975609</v>
       </c>
       <c r="N16" s="15">
         <v>-92.307692307692</v>
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-83.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>40</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I17" s="14">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J17" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K17" s="15">
-        <v>15.217391304347</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L17" s="15">
-        <v>29.268292682926</v>
+        <v>21.739130434782</v>
       </c>
       <c r="M17" s="15">
-        <v>488.888888888889</v>
+        <v>522.222222222222</v>
       </c>
       <c r="N17" s="15">
-        <v>12.765957446808</v>
+        <v>14.285714285714</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J18" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K18" s="15">
-        <v>-34.375</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="L18" s="15">
-        <v>-46.153846153846</v>
+        <v>-45.238095238095</v>
       </c>
       <c r="M18" s="15">
-        <v>-55.319148936170</v>
+        <v>-54</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.947368421052</v>
+        <v>-88.669950738916</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>-73.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G19" s="14">
         <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>-47.368421052631</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="I19" s="14">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J19" s="14">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="K19" s="15">
-        <v>-33.027522935779</v>
+        <v>-30.701754385964</v>
       </c>
       <c r="L19" s="15">
-        <v>-37.606837606837</v>
+        <v>-40.151515151515</v>
       </c>
       <c r="M19" s="15">
-        <v>-35.964912280701</v>
+        <v>-34.710743801652</v>
       </c>
       <c r="N19" s="15">
-        <v>-38.135593220339</v>
+        <v>-37.301587301587</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
         <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I20" s="14">
         <v>17</v>
       </c>
       <c r="J20" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>54.545454545454</v>
+        <v>30.769230769230</v>
       </c>
       <c r="L20" s="15">
-        <v>-56.410256410256</v>
+        <v>-62.222222222222</v>
       </c>
       <c r="M20" s="15">
-        <v>-15</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.603174603174</v>
+        <v>-94.970414201183</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-52</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F21" s="17">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="G21" s="17">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>-20</v>
+        <v>-28.985507246376</v>
       </c>
       <c r="I21" s="17">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="J21" s="17">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.567567567567</v>
+        <v>-17.021276595744</v>
       </c>
       <c r="L21" s="18">
-        <v>-31.970260223048</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.087336244541</v>
+        <v>-20.731707317073</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.689234184239</v>
+        <v>-79.6875</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="14">
+      <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="14">
         <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="L22" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M22" s="15">
-        <v>-12.5</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,20 +1223,20 @@
       <c r="C23" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D23" s="14">
-        <v>3</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F23" s="14">
-        <v>1</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G23" s="14">
         <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I23" s="14">
         <v>3</v>
@@ -1248,7 +1248,7 @@
         <v>-50</v>
       </c>
       <c r="L23" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M23" s="15">
         <v>50</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E24" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
         <v>65</v>
       </c>
       <c r="G24" s="14">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="H24" s="15">
-        <v>-38.095238095238</v>
+        <v>-32.291666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="J24" s="14">
-        <v>369</v>
+        <v>388</v>
       </c>
       <c r="K24" s="15">
-        <v>-24.119241192411</v>
+        <v>-23.195876288659</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.097902097902</v>
+        <v>-6.289308176100</v>
       </c>
       <c r="M24" s="15">
-        <v>31.455399061032</v>
+        <v>29.004329004329</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D25" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E25" s="15">
-        <v>-35.714285714285</v>
+        <v>-6.25</v>
       </c>
       <c r="F25" s="14">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="G25" s="14">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="H25" s="15">
-        <v>-47.692307692307</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="I25" s="14">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="J25" s="14">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.846153846153</v>
+        <v>-32.246376811594</v>
       </c>
       <c r="L25" s="15">
-        <v>-11.340206185567</v>
+        <v>-13.425925925925</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" s="14">
         <v>18</v>
       </c>
       <c r="H26" s="15">
-        <v>27.777777777777</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J26" s="14">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K26" s="15">
-        <v>3.125</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>15.789473684210</v>
+        <v>14.754098360655</v>
       </c>
       <c r="M26" s="15">
-        <v>11.864406779661</v>
+        <v>11.111111111111</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>7</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>600</v>
       </c>
       <c r="F28" s="14">
+        <v>7</v>
+      </c>
+      <c r="G28" s="14">
         <v>1</v>
       </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
+      <c r="H28" s="15">
+        <v>600</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>-18.181818181818</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L28" s="15">
-        <v>-62.5</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-078pct.xlsx
+++ b/data/source/weekly/cs-en-us-078pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -926,7 +926,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-75</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="E16" s="15">
-        <v>-50</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-12.5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J16" s="14">
         <v>22</v>
       </c>
       <c r="K16" s="15">
-        <v>-18.181818181818</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L16" s="15">
-        <v>-40</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="M16" s="15">
-        <v>-56.097560975609</v>
+        <v>-57.446808510638</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.307692307692</v>
+        <v>-92.063492063492</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>5</v>
+      </c>
+      <c r="D17" s="14">
         <v>2</v>
       </c>
-      <c r="D17" s="14">
-        <v>3</v>
-      </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>150</v>
       </c>
       <c r="F17" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
         <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>-7.692307692307</v>
+        <v>7.692307692307</v>
       </c>
       <c r="I17" s="14">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J17" s="14">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="K17" s="15">
-        <v>14.285714285714</v>
+        <v>19.607843137254</v>
       </c>
       <c r="L17" s="15">
-        <v>21.739130434782</v>
+        <v>32.608695652173</v>
       </c>
       <c r="M17" s="15">
-        <v>522.222222222222</v>
+        <v>577.777777777778</v>
       </c>
       <c r="N17" s="15">
-        <v>14.285714285714</v>
+        <v>10.909090909090</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F18" s="14">
+        <v>8</v>
+      </c>
+      <c r="G18" s="14">
+        <v>4</v>
+      </c>
+      <c r="H18" s="15">
         <v>100</v>
       </c>
-      <c r="F18" s="14">
-        <v>6</v>
-      </c>
-      <c r="G18" s="14">
-        <v>6</v>
-      </c>
-      <c r="H18" s="15">
-        <v>0</v>
-      </c>
       <c r="I18" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J18" s="14">
         <v>33</v>
       </c>
       <c r="K18" s="15">
-        <v>-30.303030303030</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="L18" s="15">
-        <v>-45.238095238095</v>
+        <v>-40.476190476190</v>
       </c>
       <c r="M18" s="15">
-        <v>-54</v>
+        <v>-51.923076923076</v>
       </c>
       <c r="N18" s="15">
-        <v>-88.669950738916</v>
+        <v>-89.130434782608</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="F19" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G19" s="14">
         <v>38</v>
       </c>
       <c r="H19" s="15">
-        <v>-52.631578947368</v>
+        <v>-44.736842105263</v>
       </c>
       <c r="I19" s="14">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J19" s="14">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="K19" s="15">
-        <v>-30.701754385964</v>
+        <v>-28.688524590163</v>
       </c>
       <c r="L19" s="15">
-        <v>-40.151515151515</v>
+        <v>-38.732394366197</v>
       </c>
       <c r="M19" s="15">
-        <v>-34.710743801652</v>
+        <v>-33.076923076923</v>
       </c>
       <c r="N19" s="15">
-        <v>-37.301587301587</v>
+        <v>-32.03125</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
+        <v>4</v>
+      </c>
+      <c r="G20" s="14">
         <v>5</v>
       </c>
-      <c r="G20" s="14">
-        <v>3</v>
-      </c>
       <c r="H20" s="15">
-        <v>66.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J20" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K20" s="15">
-        <v>30.769230769230</v>
+        <v>20</v>
       </c>
       <c r="L20" s="15">
-        <v>-62.222222222222</v>
+        <v>-64</v>
       </c>
       <c r="M20" s="15">
-        <v>-26.086956521739</v>
+        <v>-25</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.970414201183</v>
+        <v>-94.986072423398</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>-23.076923076923</v>
+        <v>41.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.985507246376</v>
+        <v>-16.417910447761</v>
       </c>
       <c r="I21" s="17">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="J21" s="17">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.021276595744</v>
+        <v>-13.765182186234</v>
       </c>
       <c r="L21" s="18">
-        <v>-34.782608695652</v>
+        <v>-32.380952380952</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.731707317073</v>
+        <v>-19.318181818181</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.6875</v>
+        <v>-79.420289855072</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>-80</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
         <v>10</v>
       </c>
       <c r="K22" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>-11.111111111111</v>
+        <v>11.111111111111</v>
       </c>
       <c r="M22" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1229,29 +1229,29 @@
       <c r="E23" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="13" t="s">
-        <v>20</v>
+      <c r="F23" s="14">
+        <v>1</v>
       </c>
       <c r="G23" s="14">
         <v>3</v>
       </c>
       <c r="H23" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J23" s="14">
         <v>6</v>
       </c>
       <c r="K23" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L23" s="15">
-        <v>-57.142857142857</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="M23" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="F24" s="14">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="G24" s="14">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="H24" s="15">
-        <v>-32.291666666666</v>
+        <v>-31.868131868131</v>
       </c>
       <c r="I24" s="14">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="J24" s="14">
-        <v>388</v>
+        <v>416</v>
       </c>
       <c r="K24" s="15">
-        <v>-23.195876288659</v>
+        <v>-24.759615384615</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.289308176100</v>
+        <v>-6.567164179104</v>
       </c>
       <c r="M24" s="15">
-        <v>29.004329004329</v>
+        <v>25.2</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D25" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="E25" s="15">
-        <v>-6.25</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F25" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G25" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="H25" s="15">
-        <v>-35.483870967741</v>
+        <v>-38.805970149253</v>
       </c>
       <c r="I25" s="14">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="J25" s="14">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="K25" s="15">
-        <v>-32.246376811594</v>
+        <v>-33.221476510067</v>
       </c>
       <c r="L25" s="15">
-        <v>-13.425925925925</v>
+        <v>-12.334801762114</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
-      </c>
-      <c r="D26" s="14">
         <v>6</v>
       </c>
-      <c r="E26" s="15">
-        <v>-16.666666666666</v>
+      <c r="D26" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F26" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G26" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="H26" s="15">
-        <v>33.333333333333</v>
+        <v>75</v>
       </c>
       <c r="I26" s="14">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="J26" s="14">
         <v>70</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>8.571428571428</v>
       </c>
       <c r="L26" s="15">
-        <v>14.754098360655</v>
+        <v>13.432835820895</v>
       </c>
       <c r="M26" s="15">
-        <v>11.111111111111</v>
+        <v>20.634920634920</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="F28" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="I28" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>33.333333333333</v>
+        <v>46.153846153846</v>
       </c>
       <c r="L28" s="15">
-        <v>-42.857142857142</v>
+        <v>-36.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-078pct.xlsx
+++ b/data/source/weekly/cs-en-us-078pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -901,14 +901,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>2</v>
@@ -926,48 +926,48 @@
         <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>33.333333333333</v>
+        <v>20</v>
       </c>
       <c r="I16" s="14">
         <v>20</v>
       </c>
       <c r="J16" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>-9.090909090909</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="L16" s="15">
-        <v>-35.483870967741</v>
+        <v>-37.5</v>
       </c>
       <c r="M16" s="15">
-        <v>-57.446808510638</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.063492063492</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>7.692307692307</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="J17" s="14">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K17" s="15">
-        <v>19.607843137254</v>
+        <v>23.076923076923</v>
       </c>
       <c r="L17" s="15">
-        <v>32.608695652173</v>
+        <v>30.612244897959</v>
       </c>
       <c r="M17" s="15">
-        <v>577.777777777778</v>
+        <v>611.111111111111</v>
       </c>
       <c r="N17" s="15">
-        <v>10.909090909090</v>
+        <v>1.587301587301</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>3</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>100</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>-24.242424242424</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="L18" s="15">
-        <v>-40.476190476190</v>
+        <v>-42.222222222222</v>
       </c>
       <c r="M18" s="15">
-        <v>-51.923076923076</v>
+        <v>-53.571428571428</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.130434782608</v>
+        <v>-89.430894308943</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,13 +1057,13 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E19" s="15">
-        <v>-12.5</v>
+        <v>-40</v>
       </c>
       <c r="F19" s="14">
         <v>21</v>
@@ -1075,22 +1075,22 @@
         <v>-44.736842105263</v>
       </c>
       <c r="I19" s="14">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="J19" s="14">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K19" s="15">
-        <v>-28.688524590163</v>
+        <v>-29.545454545454</v>
       </c>
       <c r="L19" s="15">
-        <v>-38.732394366197</v>
+        <v>-38</v>
       </c>
       <c r="M19" s="15">
-        <v>-33.076923076923</v>
+        <v>-34.507042253521</v>
       </c>
       <c r="N19" s="15">
-        <v>-32.03125</v>
+        <v>-30.075187969924</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="E20" s="15">
-        <v>-50</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
+        <v>5</v>
+      </c>
+      <c r="G20" s="14">
         <v>4</v>
       </c>
-      <c r="G20" s="14">
-        <v>5</v>
-      </c>
       <c r="H20" s="15">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="I20" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J20" s="14">
         <v>15</v>
       </c>
       <c r="K20" s="15">
-        <v>20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L20" s="15">
-        <v>-64</v>
+        <v>-60</v>
       </c>
       <c r="M20" s="15">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.986072423398</v>
+        <v>-94.652406417112</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>41.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="F21" s="17">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.417910447761</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I21" s="17">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="J21" s="17">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.765182186234</v>
+        <v>-14.122137404580</v>
       </c>
       <c r="L21" s="18">
-        <v>-32.380952380952</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.318181818181</v>
+        <v>-19.928825622775</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.420289855072</v>
+        <v>-79.319852941176</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1192,10 +1192,10 @@
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
@@ -1220,8 +1220,8 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>1</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" s="14">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E24" s="15">
-        <v>-46.428571428571</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F24" s="14">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G24" s="14">
         <v>91</v>
       </c>
       <c r="H24" s="15">
-        <v>-31.868131868131</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I24" s="14">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="J24" s="14">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="K24" s="15">
-        <v>-24.759615384615</v>
+        <v>-25.565610859728</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.567164179104</v>
+        <v>-7.323943661971</v>
       </c>
       <c r="M24" s="15">
-        <v>25.2</v>
+        <v>24.150943396226</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D25" s="14">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E25" s="15">
-        <v>-45.454545454545</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F25" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G25" s="14">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.805970149253</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="I25" s="14">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="J25" s="14">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.221476510067</v>
+        <v>-33.012820512820</v>
       </c>
       <c r="L25" s="15">
-        <v>-12.334801762114</v>
+        <v>-12.552301255230</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
-      </c>
-      <c r="D26" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D26" s="14">
+        <v>8</v>
+      </c>
+      <c r="E26" s="15">
+        <v>-50</v>
       </c>
       <c r="F26" s="14">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="G26" s="14">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="H26" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="J26" s="14">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K26" s="15">
-        <v>8.571428571428</v>
+        <v>2.564102564102</v>
       </c>
       <c r="L26" s="15">
-        <v>13.432835820895</v>
+        <v>12.676056338028</v>
       </c>
       <c r="M26" s="15">
-        <v>20.634920634920</v>
+        <v>23.076923076923</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,14 +1393,14 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>1</v>
-      </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-50</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
         <v>3</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
       <c r="E28" s="15">
-        <v>200</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>400</v>
+        <v>140</v>
       </c>
       <c r="I28" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K28" s="15">
-        <v>46.153846153846</v>
+        <v>31.25</v>
       </c>
       <c r="L28" s="15">
-        <v>-36.666666666666</v>
+        <v>-34.375</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-078pct.xlsx
+++ b/data/source/weekly/cs-en-us-078pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
+      </c>
+      <c r="F15" s="14">
+        <v>1</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>2</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="L15" s="15">
         <v>0</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-100</v>
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H16" s="15">
-        <v>20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J16" s="14">
         <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>-13.043478260869</v>
+        <v>-8.695652173913</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.5</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="M16" s="15">
-        <v>-58.333333333333</v>
+        <v>-58</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.307692307692</v>
+        <v>-92.363636363636</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H17" s="15">
-        <v>-8.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I17" s="14">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J17" s="14">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K17" s="15">
-        <v>23.076923076923</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L17" s="15">
-        <v>30.612244897959</v>
+        <v>26.923076923076</v>
       </c>
       <c r="M17" s="15">
-        <v>611.111111111111</v>
+        <v>560</v>
       </c>
       <c r="N17" s="15">
-        <v>1.587301587301</v>
+        <v>-7.042253521126</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E18" s="15">
-        <v>-66.666666666666</v>
+        <v>-40</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>16.666666666666</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.777777777777</v>
+        <v>-29.268292682926</v>
       </c>
       <c r="L18" s="15">
-        <v>-42.222222222222</v>
+        <v>-35.555555555555</v>
       </c>
       <c r="M18" s="15">
-        <v>-53.571428571428</v>
+        <v>-53.225806451612</v>
       </c>
       <c r="N18" s="15">
-        <v>-89.430894308943</v>
+        <v>-88.671875</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-40</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>-44.736842105263</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="J19" s="14">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="K19" s="15">
-        <v>-29.545454545454</v>
+        <v>-25.899280575539</v>
       </c>
       <c r="L19" s="15">
-        <v>-38</v>
+        <v>-35.625</v>
       </c>
       <c r="M19" s="15">
-        <v>-34.507042253521</v>
+        <v>-29.452054794520</v>
       </c>
       <c r="N19" s="15">
-        <v>-30.075187969924</v>
+        <v>-27.972027972028</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>300</v>
       </c>
       <c r="F20" s="14">
+        <v>7</v>
+      </c>
+      <c r="G20" s="14">
         <v>5</v>
       </c>
-      <c r="G20" s="14">
-        <v>4</v>
-      </c>
       <c r="H20" s="15">
+        <v>40</v>
+      </c>
+      <c r="I20" s="14">
         <v>25</v>
       </c>
-      <c r="I20" s="14">
-        <v>20</v>
-      </c>
       <c r="J20" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" s="15">
-        <v>33.333333333333</v>
+        <v>56.25</v>
       </c>
       <c r="L20" s="15">
-        <v>-60</v>
+        <v>-50.980392156862</v>
       </c>
       <c r="M20" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-94.652406417112</v>
+        <v>-93.654822335025</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-20</v>
+        <v>18.75</v>
       </c>
       <c r="F21" s="17">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G21" s="17">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="H21" s="18">
-        <v>-23.076923076923</v>
+        <v>1.785714285714</v>
       </c>
       <c r="I21" s="17">
-        <v>225</v>
+        <v>246</v>
       </c>
       <c r="J21" s="17">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.122137404580</v>
+        <v>-11.510791366906</v>
       </c>
       <c r="L21" s="18">
-        <v>-31.818181818181</v>
+        <v>-28.695652173913</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.928825622775</v>
+        <v>-16.610169491525</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.319852941176</v>
+        <v>-78.627280625543</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,29 +1182,29 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I22" s="14">
         <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L22" s="15">
         <v>11.111111111111</v>
@@ -1232,11 +1232,11 @@
       <c r="F23" s="14">
         <v>1</v>
       </c>
-      <c r="G23" s="14">
-        <v>3</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-66.666666666666</v>
+      <c r="G23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I23" s="14">
         <v>4</v>
@@ -1251,7 +1251,7 @@
         <v>-42.857142857142</v>
       </c>
       <c r="M23" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D24" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>-38.461538461538</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="F24" s="14">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="G24" s="14">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="H24" s="15">
-        <v>-28.571428571428</v>
+        <v>-28.846153846153</v>
       </c>
       <c r="I24" s="14">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="J24" s="14">
-        <v>442</v>
+        <v>473</v>
       </c>
       <c r="K24" s="15">
-        <v>-25.565610859728</v>
+        <v>-25.792811839323</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.323943661971</v>
+        <v>-6.4</v>
       </c>
       <c r="M24" s="15">
-        <v>24.150943396226</v>
+        <v>25.357142857142</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>12</v>
+      </c>
+      <c r="D25" s="14">
         <v>11</v>
       </c>
-      <c r="D25" s="14">
-        <v>14</v>
-      </c>
       <c r="E25" s="15">
-        <v>-21.428571428571</v>
+        <v>9.090909090909</v>
       </c>
       <c r="F25" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G25" s="14">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="H25" s="15">
-        <v>-30.303030303030</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I25" s="14">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="J25" s="14">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="K25" s="15">
-        <v>-33.012820512820</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="L25" s="15">
-        <v>-12.552301255230</v>
+        <v>-12.301587301587</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>5</v>
+      </c>
+      <c r="D26" s="14">
         <v>4</v>
       </c>
-      <c r="D26" s="14">
-        <v>8</v>
-      </c>
       <c r="E26" s="15">
-        <v>-50</v>
+        <v>25</v>
       </c>
       <c r="F26" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G26" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I26" s="14">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J26" s="14">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="K26" s="15">
-        <v>2.564102564102</v>
+        <v>3.658536585365</v>
       </c>
       <c r="L26" s="15">
-        <v>12.676056338028</v>
+        <v>16.438356164383</v>
       </c>
       <c r="M26" s="15">
-        <v>23.076923076923</v>
+        <v>26.865671641791</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
+      </c>
+      <c r="F27" s="14">
+        <v>1</v>
+      </c>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
       </c>
       <c r="J27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="15">
-        <v>-40</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
         <v>-50</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>12</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="15">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="I28" s="14">
         <v>21</v>
       </c>
       <c r="J28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" s="15">
-        <v>31.25</v>
+        <v>23.529411764705</v>
       </c>
       <c r="L28" s="15">
-        <v>-34.375</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>2</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>100</v>
       </c>
       <c r="L29" s="15">
         <v>-33.333333333333</v>
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>2</v>
       </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>100</v>
       </c>
       <c r="L30" s="15">
         <v>-33.333333333333</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,13 +1567,13 @@
         <v>21</v>
       </c>
       <c r="I31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="14">
         <v>2</v>
       </c>
       <c r="K31" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>
